--- a/stories/arbres/ATOM-JEU.FOOT.001-04.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Loïc et maman sont au parc. Maman pose deux sacs. C'est le but. Elle trace un rectangle. Maman dit : voici l'espace montré. On reste dans l'espace montré. Loïc touche le ballon. Maman dit : on va passer le ballon. Puis on vise le but. Loïc passe. Maman rend. Loïc pousse le ballon vers le but. Les pieds restent dans l'espace montré.</t>
+          <t>Loïc et maman sont au parc. Maman pose deux sacs. C'est le but. Elle trace un rectangle. Voici l'espace montré. On reste dans l'espace montré. Loïc touche le ballon. On va passer le ballon. Puis on vise le but. Loïc passe. Maman rend. Loïc pousse le ballon vers le but. Les pieds restent dans l'espace montré.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Loïc et maman sont au parc. Maman pose deux sacs. C'est le but. Elle trace un rectangle.
+maman|Voici l'espace montré. On reste dans l'espace montré.
+narrateur|Loïc touche le ballon.
+maman|On va passer le ballon.
+narrateur|Puis on vise le but. Loïc passe. Maman rend. Loïc pousse le ballon vers le but. Les pieds restent dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Loïc joue au foot. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Loïc a passé le ballon. Il a visé le but. Dans l'espace montré.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman range les sacs. Loïc boit une gorgée.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.FOOT.001-04.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Puis on vise le but. Loïc passe. Maman rend. Loïc pousse le ballon vers le but. Les pieds restent dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Loïc joue au foot. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|Loïc a passé le ballon. Il a visé le but. Dans l'espace montré.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1843,7 @@
           <t>narrateur|Maman range les sacs. Loïc boit une gorgée.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.FOOT.001-04.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Loïc vise le but au parc</t>
+          <t>La coccinelle du banc</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JEU.REG.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une coccinelle marche sur le banc tiède. Raphaël se passe le ballon avec maman. Il vise le but. Il reste dans l'espace montré.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Loïc et maman sont au parc. Maman pose deux sacs. C'est le but. Elle trace un rectangle. Voici l'espace montré. On reste dans l'espace montré. Loïc touche le ballon. On va passer le ballon. Puis on vise le but. Loïc passe. Maman rend. Loïc pousse le ballon vers le but. Les pieds restent dans l'espace montré.</t>
+          <t>Le banc de bois est tiède. Une petite coccinelle marche sur le dossier. Elle a des points noirs. Au loin, une balançoire grince. Crr. Crr. L'air sent l'herbe coupée. Une pomme de pin est sous le banc. Elle est sèche et piquante. Tu la vois, Raphaël ? Elle pique. Oui. On la laisse. Raphaël pose la main sur le bois. Le banc est chaud. Le soleil l'a chauffé. Un oiseau chante, tout près. Il est caché. Dans l'arbre, oui. Tu as vu la coccinelle, Raphaël ? Elle est rouge. Elle est toute petite. Oui. Elle va tout doux. Maman pose le sac contre le banc. En ce moment, Raphaël est au parc. Maman pose deux sacs. C'est le but. Elle trace un rectangle. Voici l'espace montré. On reste dans l'espace montré. Raphaël touche le ballon. Il est souple et un peu chaud. On va passer le ballon. Puis on vise le but. Raphaël passe. Maman rend. Bravo. Tu as passé. Raphaël pousse le ballon vers le but. Les pieds restent dans l'espace montré. Le ballon roule entre les sacs. Dedans ! Bravo, Raphaël. Tu as visé le but. La coccinelle est encore sur le banc. On reste dans le rectangle. Oui, maman. Raphaël ramène le ballon. Il passe encore. Maman rend. Il vise encore le but. La balançoire grince plus loin. Un dernier passage ? Oui. Raphaël passe. Maman rend. Raphaël pousse vers le but. Le ballon roule entre les sacs. Bravo. Tu as passé. Tu as visé le but. Dans l'espace montré.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1329,69 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Loïc et maman sont au parc. Maman pose deux sacs. C'est le but. Elle trace un rectangle.
-maman|Voici l'espace montré. On reste dans l'espace montré.
-narrateur|Loïc touche le ballon.
+          <t>narrateur|Le banc de bois est tiède.
+narrateur|Une petite coccinelle marche sur le dossier.
+narrateur|Elle a des points noirs.
+narrateur|Au loin, une balançoire grince.
+narrateur|Crr.
+narrateur|Crr.
+narrateur|L'air sent l'herbe coupée.
+narrateur|Une pomme de pin est sous le banc.
+narrateur|Elle est sèche et piquante.
+maman|Tu la vois, Raphaël ?
+enfant-m|Elle pique.
+maman|Oui.
+maman|On la laisse.
+narrateur|Raphaël pose la main sur le bois.
+enfant-m|Le banc est chaud.
+maman|Le soleil l'a chauffé.
+narrateur|Un oiseau chante, tout près.
+enfant-m|Il est caché.
+maman|Dans l'arbre, oui.
+maman|Tu as vu la coccinelle, Raphaël ?
+enfant-m|Elle est rouge.
+enfant-m|Elle est toute petite.
+maman|Oui.
+maman|Elle va tout doux.
+narrateur|Maman pose le sac contre le banc.
+narrateur|En ce moment, Raphaël est au parc.
+narrateur|Maman pose deux sacs.
+narrateur|C'est le but.
+narrateur|Elle trace un rectangle.
+maman|Voici l'espace montré.
+maman|On reste dans l'espace montré.
+narrateur|Raphaël touche le ballon.
+narrateur|Il est souple et un peu chaud.
 maman|On va passer le ballon.
-narrateur|Puis on vise le but. Loïc passe. Maman rend. Loïc pousse le ballon vers le but. Les pieds restent dans l'espace montré.</t>
+maman|Puis on vise le but.
+narrateur|Raphaël passe.
+narrateur|Maman rend.
+maman|Bravo.
+maman|Tu as passé.
+narrateur|Raphaël pousse le ballon vers le but.
+narrateur|Les pieds restent dans l'espace montré.
+narrateur|Le ballon roule entre les sacs.
+enfant-m|Dedans !
+maman|Bravo, Raphaël.
+maman|Tu as visé le but.
+narrateur|La coccinelle est encore sur le banc.
+maman|On reste dans le rectangle.
+enfant-m|Oui, maman.
+narrateur|Raphaël ramène le ballon.
+narrateur|Il passe encore.
+narrateur|Maman rend.
+narrateur|Il vise encore le but.
+narrateur|La balançoire grince plus loin.
+maman|Un dernier passage ?
+enfant-m|Oui.
+narrateur|Raphaël passe.
+narrateur|Maman rend.
+narrateur|Raphaël pousse vers le but.
+narrateur|Le ballon roule entre les sacs.
+maman|Bravo.
+maman|Tu as passé.
+maman|Tu as visé le but.
+maman|Dans l'espace montré.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,7 +1423,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Loïc joue au foot. Que fait-il ?</t>
+          <t>Raphaël joue au foot. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1579,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Loïc joue au foot. Que fait-il ?</t>
+          <t>narrateur|Raphaël joue au foot.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1608,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Loïc a passé le ballon. Il a visé le but. Dans l'espace montré.</t>
+          <t>Raphaël a passé le ballon. Il a visé le but. Dans l'espace montré. Tu as passé, Raphaël. Bravo. Tu as visé le but. Dans l'espace montré.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1752,13 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Loïc a passé le ballon. Il a visé le but. Dans l'espace montré.</t>
+          <t>narrateur|Raphaël a passé le ballon.
+narrateur|Il a visé le but.
+narrateur|Dans l'espace montré.
+maman|Tu as passé, Raphaël.
+maman|Bravo.
+maman|Tu as visé le but.
+enfant-m|Dans l'espace montré.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1786,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range les sacs. Loïc boit une gorgée.</t>
+          <t>Maman range les sacs. Raphaël boit une gorgée. Le banc est encore tiède. La coccinelle n'est plus là. Elle est partie. Oui. Elle a fini sa promenade. Tu as visé le but. Oui, maman. J'ai passé. Dans l'espace montré. Bravo. Tu as fait du bon travail. Ils marchent vers la maison. La balançoire grince encore, tout loin. La pomme de pin reste sous le banc. Elle pique encore. Oui. Tu as passé. Tu as visé le but. Dans l'espace montré. C'est ça. Le bois du banc refroidit un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,10 +1922,36 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman range les sacs. Loïc boit une gorgée.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Maman range les sacs.
+narrateur|Raphaël boit une gorgée.
+narrateur|Le banc est encore tiède.
+narrateur|La coccinelle n'est plus là.
+enfant-m|Elle est partie.
+maman|Oui.
+maman|Elle a fini sa promenade.
+maman|Tu as visé le but.
+enfant-m|Oui, maman.
+enfant-m|J'ai passé.
+enfant-m|Dans l'espace montré.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Ils marchent vers la maison.
+narrateur|La balançoire grince encore, tout loin.
+narrateur|La pomme de pin reste sous le banc.
+enfant-m|Elle pique encore.
+maman|Oui.
+maman|Tu as passé.
+maman|Tu as visé le but.
+enfant-m|Dans l'espace montré.
+maman|C'est ça.
+narrateur|Le bois du banc refroidit un peu.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,7 +1976,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le banc de bois reste tiède. J'ai passé. J'ai visé le but. Bravo, Raphaël. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2116,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le banc de bois reste tiède.
+enfant-m|J'ai passé.
+enfant-m|J'ai visé le but.
+maman|Bravo, Raphaël.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2180,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.FOOT.001-04.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-04.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Loïc et maman sont au parc. Maman pose deux sacs. C'est le &lt;emphasis level="moderate"&gt;but&lt;/emphasis&gt;. Elle trace un rectangle. Maman dit : voici l'espace montré. On reste dans l'espace montré. Loïc touche le ballon. Maman dit : on va passer le ballon. Puis on vise le but. Loïc passe. Maman rend. Loïc pousse le ballon vers le but. Les pieds restent dans l'espace montré.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le banc de bois est tiède. Une petite coccinelle marche sur le dossier. Elle a des points noirs. Au loin, une balançoire grince. Crr. Crr. L'air sent l'herbe coupée. Une pomme de pin est sous le banc. Elle est sèche et piquante. Tu la vois, Raphaël ? Elle pique. Oui. On la laisse. Raphaël pose la main sur le bois. Le banc est chaud. Le soleil l'a chauffé. Un oiseau chante, tout près. Il est caché. Dans l'arbre, oui. Tu as vu la coccinelle, Raphaël ? Elle est rouge. Elle est toute petite. Oui. Elle va tout doux. Maman pose le sac contre le banc. En ce moment, Raphaël est au parc. Maman pose deux sacs. C'est le but. Elle trace un rectangle. Voici l'espace montré. On reste dans l'espace montré. Raphaël touche le ballon. Il est souple et un peu chaud. On va passer le ballon. Puis on vise le but. Raphaël passe. Maman rend. Bravo. Tu as passé. Raphaël pousse le ballon vers le but. Les pieds restent dans l'espace montré. Le ballon roule entre les sacs. Dedans ! Bravo, Raphaël. Tu as visé le but. La coccinelle est encore sur le banc. On reste dans le rectangle. Oui, maman. Raphaël ramène le ballon. Il passe encore. Maman rend. Il vise encore le but. La balançoire grince plus loin. Un dernier passage ? Oui. Raphaël passe. Maman rend. Raphaël pousse vers le but. Le ballon roule entre les sacs. Bravo. Tu as passé. Tu as visé le but. Dans l'espace montré.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Loïc joue au foot. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël joue au foot. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1583,7 +1583,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1613,7 +1612,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Loïc a passé le ballon. Il a visé le &lt;emphasis level="moderate"&gt;but&lt;/emphasis&gt;. Dans l'espace montré.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a passé le ballon. Il a visé le but. Dans l'espace montré. Tu as passé, Raphaël. Bravo. Tu as visé le but. Dans l'espace montré.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1761,7 +1760,6 @@
 enfant-m|Dans l'espace montré.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1786,12 +1784,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman range les sacs. Raphaël boit une gorgée. Le banc est encore tiède. La coccinelle n'est plus là. Elle est partie. Oui. Elle a fini sa promenade. Tu as visé le but. Oui, maman. J'ai passé. Dans l'espace montré. Bravo. Tu as fait du bon travail. Ils marchent vers la maison. La balançoire grince encore, tout loin. La pomme de pin reste sous le banc. Elle pique encore. Oui. Tu as passé. Tu as visé le but. Dans l'espace montré. C'est ça. Le bois du banc refroidit un peu.</t>
+          <t>Maman range les sacs. Raphaël boit une gorgée. Le banc est encore tiède. La coccinelle n'est plus là. Elle est partie. Oui. Elle a fini sa promenade. Tu as visé le but. Oui, maman. J'ai passé. Dans l'espace montré. Bravo. Ils marchent vers la maison. La balançoire grince encore, tout loin. La pomme de pin reste sous le banc. Elle pique encore. Oui. Tu as passé. Tu as visé le but. Dans l'espace montré. C'est ça. Le bois du banc refroidit un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman range les sacs. Loïc boit une gorgée.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman range les sacs. Raphaël boit une gorgée. Le banc est encore tiède. La coccinelle n'est plus là. Elle est partie. Oui. Elle a fini sa promenade. Tu as visé le but. Oui, maman. J'ai passé. Dans l'espace montré. Bravo. Ils marchent vers la maison. La balançoire grince encore, tout loin. La pomme de pin reste sous le banc. Elle pique encore. Oui. Tu as passé. Tu as visé le but. Dans l'espace montré. C'est ça. Le bois du banc refroidit un peu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1934,7 +1932,6 @@
 enfant-m|J'ai passé.
 enfant-m|Dans l'espace montré.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 narrateur|Ils marchent vers la maison.
 narrateur|La balançoire grince encore, tout loin.
 narrateur|La pomme de pin reste sous le banc.
@@ -1976,12 +1973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le banc de bois reste tiède. J'ai passé. J'ai visé le but. Bravo, Raphaël. L'histoire est finie.</t>
+          <t>Le banc de bois reste tiède. J'ai passé. J'ai visé le but. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le banc de bois reste tiède. J'ai passé. J'ai visé le but. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2119,11 +2116,9 @@
           <t>narrateur|Le banc de bois reste tiède.
 enfant-m|J'ai passé.
 enfant-m|J'ai visé le but.
-maman|Bravo, Raphaël.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo, Raphaël.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2142,7 +2137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2187,6 +2182,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.FOOT.001-04.xlsx
+++ b/stories/arbres/ATOM-JEU.FOOT.001-04.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Loïc, maman</t>
+          <t>Raphaël, maman</t>
         </is>
       </c>
     </row>
